--- a/AAAGameData/DataTables/VariableExperimentTable.xlsx
+++ b/AAAGameData/DataTables/VariableExperimentTable.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
   <si>
     <t>#</t>
   </si>
@@ -103,13 +103,13 @@
     <t>Lv_3</t>
   </si>
   <si>
+    <t>第4关变量试验</t>
+  </si>
+  <si>
+    <t>Lv_4</t>
+  </si>
+  <si>
     <t>VariableRule_Default</t>
-  </si>
-  <si>
-    <t>第4关变量试验</t>
-  </si>
-  <si>
-    <t>Lv_4</t>
   </si>
   <si>
     <t>第5关变量试验</t>
@@ -588,154 +588,154 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" applyFill="0" borderId="0" applyBorder="0"/>
-    <xf numFmtId="43" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="2" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="3" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="0" fillId="2" applyFill="1" borderId="1" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="4" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="5" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="6" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="7" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="3" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="3" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="14" applyFont="1" fillId="0" applyFill="0" borderId="7" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="15" applyFont="1" fillId="0" applyFill="0" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="16" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -985,18 +985,18 @@
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="2"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
       <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="0"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="0"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
       <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="2"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
       <tableStyleElement type="firstRowSubheading" dxfId="10"/>
       <tableStyleElement type="secondRowSubheading" dxfId="9"/>
       <tableStyleElement type="pageFieldLabels" dxfId="8"/>
@@ -1267,7 +1267,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable=" xr">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="5"/>
@@ -1280,159 +1280,159 @@
     <col min="6" max="6" width="28.4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="0" t="s">
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="0">
+    <row r="5" spans="1:6">
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="0">
+    <row r="6" spans="1:6">
+      <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="0">
+    <row r="7" spans="1:6">
+      <c r="B7">
         <v>3</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
         <v>23</v>
       </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="8">
-      <c r="B8" s="0">
-        <v>4</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="0" t="s">
+    <row r="9" spans="1:6">
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" t="s">
         <v>25</v>
-      </c>
-      <c r="E8" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="0" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="0">
-        <v>5</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="0" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="D1:Z1" xr:uid="{333B974B-E198-4474-9F9F-B382171E8500}">
+    <dataValidation type="list" allowBlank="1" sqref="D1:Z1">
       <formula1>"i18n"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D3:Z3" xr:uid="{A3DB4E24-DC19-481F-B0A2-39BAA8694A2D}">
+    <dataValidation type="list" sqref="D3:Z3">
       <formula1>"int,enum,enum?,enum[],double,string,string[],bool,float,uint,short,Vector2,int4[],Vector3Int[],Vector3Int,Vector3,Vector4[],int4,Vector2[],Vector4,Fix64,Color32,Color,Vector2Int,Vector3[],Vector2Int[],Type,bool[],int[],Fix64[],long[],double[]"</formula1>
     </dataValidation>
   </dataValidations>
